--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD069CA-301E-4B7B-8CED-B07A0C99D751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959FEDB0-9CC5-4E89-B24E-76DD5DD0A299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-675" yWindow="3945" windowWidth="28830" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="2940" windowWidth="28830" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -55,37 +55,74 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>炎爆术</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#enum elementType: int{Fire=1,Water=2,Soil=3,Air=4}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>element</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>elementType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>time_cost</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>花费时间</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">
-备注
-参考名称
+元素</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+子流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+后缀id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+30+元素+流派+子流派+后缀id
+30+01+01+1+01
 </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>炎爆术</t>
-  </si>
-  <si>
-    <t>炎爆术</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>#enum elementType: int{Fire=1,Water=2,Soil=3,Air=4}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>element</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>elementType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fire</t>
+    <t>1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -183,7 +220,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +250,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -490,81 +530,135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="19.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.375" customWidth="1"/>
+    <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="3" customWidth="1"/>
+    <col min="4" max="6" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.375" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
+      <c r="H3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="11" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="11" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="str">
+        <f>"30"&amp;C5&amp;D5&amp;E5&amp;F5</f>
+        <v>300101101</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <f>G5</f>
+        <v>炎爆术</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>12</v>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>300000101</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959FEDB0-9CC5-4E89-B24E-76DD5DD0A299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D7F0E2-CE25-482C-9431-11F1746F52C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="75" yWindow="2940" windowWidth="28830" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="2" r:id="rId1"/>
+    <sheet name="元素_辅" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -123,6 +124,10 @@
   </si>
   <si>
     <t>1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -220,7 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -253,6 +258,18 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -535,7 +552,7 @@
   <cols>
     <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
     <col min="2" max="2" width="27.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="3" customWidth="1"/>
     <col min="4" max="6" width="10.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="14.375" customWidth="1"/>
@@ -612,7 +629,7 @@
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="str">
-        <f>"30"&amp;C5&amp;D5&amp;E5&amp;F5</f>
+        <f>"30"&amp; VLOOKUP(C5, 元素_辅!A:B, 2) &amp;D5&amp;E5&amp;F5</f>
         <v>300101101</v>
       </c>
       <c r="B5" s="7" t="str">
@@ -620,7 +637,7 @@
         <v>炎爆术</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>16</v>
@@ -664,4 +681,43 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964738F3-8024-4E2A-84BD-E3D75A928311}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" style="14" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="str">
+        <f>VLOOKUP(A1, 元素_辅!A:B, 2)</f>
+        <v>01</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="13"/>
+      <c r="B2" s="16"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="16"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D7F0E2-CE25-482C-9431-11F1746F52C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AFCD1E-32EC-442A-BCC2-D340729D067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="2" r:id="rId1"/>
-    <sheet name="元素_辅" sheetId="3" r:id="rId2"/>
+    <sheet name="辅表" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -128,6 +128,30 @@
   </si>
   <si>
     <t>火</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>子流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>学院</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>本源</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +575,7 @@
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="27.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28" style="3" customWidth="1"/>
     <col min="3" max="3" width="10.875" style="3" customWidth="1"/>
     <col min="4" max="6" width="10.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
@@ -629,7 +653,7 @@
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="str">
-        <f>"30"&amp; VLOOKUP(C5, 元素_辅!A:B, 2) &amp;D5&amp;E5&amp;F5</f>
+        <f>"30"&amp; VLOOKUP(C5, 辅表!A:B, 2) &amp; VLOOKUP(D5, 辅表!D:E, 2) &amp; VLOOKUP(E5, 辅表!G:H, 2) &amp;F5</f>
         <v>300101101</v>
       </c>
       <c r="B5" s="7" t="str">
@@ -640,10 +664,10 @@
         <v>22</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>16</v>
@@ -685,36 +709,80 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964738F3-8024-4E2A-84BD-E3D75A928311}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="21.375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="14" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="str">
-        <f>VLOOKUP(A1, 元素_辅!A:B, 2)</f>
-        <v>01</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="16"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="13"/>
       <c r="B3" s="16"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D3" s="13"/>
+      <c r="E3" s="16"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
       <c r="B4" s="16"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="16"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="16"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AFCD1E-32EC-442A-BCC2-D340729D067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F05387-051D-4B51-9C04-8A8B87104EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -653,7 +653,7 @@
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="str">
-        <f>"30"&amp; VLOOKUP(C5, 辅表!A:B, 2) &amp; VLOOKUP(D5, 辅表!D:E, 2) &amp; VLOOKUP(E5, 辅表!G:H, 2) &amp;F5</f>
+        <f>"30" &amp; VLOOKUP(C5, 辅表!A:B, 2) &amp; VLOOKUP(D5, 辅表!D:E, 2) &amp; VLOOKUP(E5, 辅表!G:H, 2) &amp; F5</f>
         <v>300101101</v>
       </c>
       <c r="B5" s="7" t="str">

--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F05387-051D-4B51-9C04-8A8B87104EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB8C654-F786-4FA4-B06F-6BE05E1F3ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -57,26 +57,6 @@
   </si>
   <si>
     <t>炎爆术</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>#enum elementType: int{Fire=1,Water=2,Soil=3,Air=4}</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>element</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>elementType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fire</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -152,6 +132,39 @@
   </si>
   <si>
     <t>本源</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>气</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>土</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒冰箭</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击加速</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬石皮肤</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -159,7 +172,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,14 +206,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -249,7 +254,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -266,21 +271,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -571,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
@@ -579,127 +579,168 @@
     <col min="3" max="3" width="10.875" style="3" customWidth="1"/>
     <col min="4" max="6" width="10.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.375" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8" s="8" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="11" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>20</v>
+    </row>
+    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C4, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D4, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E4, 辅表!G:H, 2, FALSE) &amp; F4</f>
+        <v>300101101</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <f>G4</f>
+        <v>炎爆术</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="3">
         <v>3</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="str">
-        <f>"30" &amp; VLOOKUP(C5, 辅表!A:B, 2) &amp; VLOOKUP(D5, 辅表!D:E, 2) &amp; VLOOKUP(E5, 辅表!G:H, 2) &amp; F5</f>
-        <v>300101101</v>
-      </c>
-      <c r="B5" s="7" t="str">
-        <f>G5</f>
-        <v>炎爆术</v>
-      </c>
-      <c r="C5" s="12" t="s">
+        <f>"30" &amp; VLOOKUP(C5, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D5, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E5, 辅表!G:H, 2, FALSE) &amp; F5</f>
+        <v>300201101</v>
+      </c>
+      <c r="B5" s="5" t="str">
+        <f t="shared" ref="B5:B7" si="0">G5</f>
+        <v>寒冰箭</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C6, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D6, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E6, 辅表!G:H, 2, FALSE) &amp; F6</f>
+        <v>300301101</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>硬石皮肤</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C7, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D7, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E7, 辅表!G:H, 2, FALSE) &amp; F7</f>
+        <v>300401101</v>
+      </c>
+      <c r="B7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>攻击加速</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="D7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -709,80 +750,104 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964738F3-8024-4E2A-84BD-E3D75A928311}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="14" customWidth="1"/>
-    <col min="8" max="8" width="15.375" style="15" customWidth="1"/>
+    <col min="1" max="1" width="15.375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H2" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="13"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="13"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="13"/>
-      <c r="B3" s="16"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="16"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="16"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="16"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="16"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="16"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="16"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="13"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="10"/>
+      <c r="B6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="10"/>
+      <c r="B8" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB8C654-F786-4FA4-B06F-6BE05E1F3ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE62906A-89CF-4855-AC39-3A363A4F40EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>id</t>
   </si>
@@ -57,10 +57,6 @@
   </si>
   <si>
     <t>炎爆术</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>time_cost</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -164,7 +160,31 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>硬石皮肤</t>
+    <t>硬石体肤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>time</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#enum levelType: int { E=1, D=2 , C=3 , B=4, A=5, S=6 }</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>levelType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -254,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -294,6 +314,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -571,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
@@ -580,160 +603,153 @@
     <col min="4" max="6" width="10.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="8" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="8" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="str">
-        <f>"30" &amp; VLOOKUP(C4, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D4, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E4, 辅表!G:H, 2, FALSE) &amp; F4</f>
-        <v>300101101</v>
-      </c>
-      <c r="B4" s="5" t="str">
-        <f>G4</f>
-        <v>炎爆术</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="str">
         <f>"30" &amp; VLOOKUP(C5, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D5, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E5, 辅表!G:H, 2, FALSE) &amp; F5</f>
-        <v>300201101</v>
+        <v>300101101</v>
       </c>
       <c r="B5" s="5" t="str">
-        <f t="shared" ref="B5:B7" si="0">G5</f>
-        <v>寒冰箭</v>
+        <f>G5</f>
+        <v>炎爆术</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I5" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="str">
         <f>"30" &amp; VLOOKUP(C6, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D6, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E6, 辅表!G:H, 2, FALSE) &amp; F6</f>
-        <v>300301101</v>
+        <v>300201101</v>
       </c>
       <c r="B6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>硬石皮肤</v>
+        <f t="shared" ref="B6:B8" si="0">G6</f>
+        <v>寒冰箭</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="F6" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="str">
         <f>"30" &amp; VLOOKUP(C7, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D7, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E7, 辅表!G:H, 2, FALSE) &amp; F7</f>
-        <v>300401101</v>
+        <v>300301101</v>
       </c>
       <c r="B7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>攻击加速</v>
+        <v>硬石体肤</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>31</v>
@@ -741,8 +757,45 @@
       <c r="H7" s="3">
         <v>3</v>
       </c>
+      <c r="I7" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C8, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D8, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E8, 辅表!G:H, 2, FALSE) &amp; F8</f>
+        <v>300401101</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>攻击加速</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -763,50 +816,50 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>23</v>
-      </c>
       <c r="H2" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="13"/>
@@ -815,10 +868,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="13"/>
@@ -827,10 +880,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="13"/>

--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFEE875-B77A-4D54-ABBF-889A116CAB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835CB953-3168-435E-B029-0C33D2F51666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="2" r:id="rId1"/>
+    <sheet name="辅表" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -41,75 +42,134 @@
     <t>name</t>
   </si>
   <si>
-    <t>stack_max</t>
-  </si>
-  <si>
-    <t>stack_time</t>
-  </si>
-  <si>
-    <t>buff_variable</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>uint key</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>dict&lt;buffattrType,int&gt;</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>层数上限</t>
-  </si>
-  <si>
-    <t>单层持续时间</t>
-  </si>
-  <si>
-    <t>&lt;修改类型,修改值&gt;</t>
-  </si>
-  <si>
-    <t>卡牌效果：车辆加速</t>
-  </si>
-  <si>
-    <t>acc_driving_variable=160000000;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>acc_driving_variable=80000000;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>acc_driving_variable=40000000;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>新手地宫演出：过桥</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>acc_driving_variable=110000000;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>新手巨物演出：加速行驶</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>acc_driving_variable=5000000;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>#enum element: int {金=1,木=2,水=3,火=4,土=5}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+元素</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+子流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+后缀id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+30+元素+流派+子流派+后缀id
+30+01+01+1+01
+</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>火</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>子流派</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>土</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>levelType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>搬运法</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>木</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>05</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>樵木鬼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#enum levelType: int { 人阶下=1, 人阶中=2, 人阶上=3, 地阶下=4, 地阶中=5, 地阶上=6, 天阶下=7, 天阶中=8, 天阶上=9 }</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>地阶下</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -128,22 +188,16 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="5"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -156,6 +210,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="6"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -193,35 +256,50 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -500,164 +578,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.25" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.125" style="4"/>
+    <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.875" style="3" customWidth="1"/>
+    <col min="4" max="6" width="10.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="8" customFormat="1" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C5, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D5, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E5, 辅表!G:H, 2, FALSE) &amp; F5</f>
+        <v>300401101</v>
+      </c>
+      <c r="B5" s="5" t="str">
+        <f>G5</f>
+        <v>樵木鬼</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="4">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4">
-        <v>9</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4">
-        <v>15</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="4">
-        <v>3</v>
-      </c>
-      <c r="D7" s="4">
-        <v>25</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>4</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>45</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>5</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="4">
-        <v>4</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1200</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="G5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964738F3-8024-4E2A-84BD-E3D75A928311}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="11" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="13"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="13"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="13"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="10"/>
+      <c r="B8" s="13"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835CB953-3168-435E-B029-0C33D2F51666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DC57DB-F500-4E9A-912A-DF471AED54FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="4245" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="2" r:id="rId1"/>
@@ -160,15 +160,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>樵木鬼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>#enum levelType: int { 人阶下=1, 人阶中=2, 人阶上=3, 地阶下=4, 地阶中=5, 地阶上=6, 天阶下=7, 天阶中=8, 天阶上=9 }</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>地阶下</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AA</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -591,7 +591,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -649,7 +649,7 @@
       </c>
       <c r="B5" s="5" t="str">
         <f>G5</f>
-        <v>樵木鬼</v>
+        <v>AA</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>29</v>
@@ -664,10 +664,10 @@
         <v>7</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">

--- a/Assets/Tables/card.xlsx
+++ b/Assets/Tables/card.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test\TestProj\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DC57DB-F500-4E9A-912A-DF471AED54FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8FC6C3-22C1-47D3-8EE6-5A0B510D3047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="4245" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="2" r:id="rId1"/>
-    <sheet name="辅表" sheetId="3" r:id="rId2"/>
+    <sheet name="deck" sheetId="5" r:id="rId2"/>
+    <sheet name="辅表" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -169,6 +170,38 @@
   </si>
   <si>
     <t>AA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>数量</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>填入：卡牌名称</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -258,7 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -298,6 +331,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -578,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
@@ -589,8 +625,8 @@
     <col min="8" max="8" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -671,24 +707,116 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="A6" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C6, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D6, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E6, 辅表!G:H, 2, FALSE) &amp; F6</f>
+        <v>300301101</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f>G6</f>
+        <v>BB</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C7, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D7, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E7, 辅表!G:H, 2, FALSE) &amp; F7</f>
+        <v>300201101</v>
+      </c>
+      <c r="B7" s="5" t="str">
+        <f t="shared" ref="B7:B8" si="0">G7</f>
+        <v>CC</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C8, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D8, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E8, 辅表!G:H, 2, FALSE) &amp; F8</f>
+        <v>300501101</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>DD</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="str">
+        <f>"30" &amp; VLOOKUP(C9, 辅表!A:B, 2, FALSE) &amp; VLOOKUP(D9, 辅表!D:E, 2, FALSE) &amp; VLOOKUP(E9, 辅表!G:H, 2, FALSE) &amp; F9</f>
+        <v>300101101</v>
+      </c>
+      <c r="B9" s="5" t="str">
+        <f t="shared" ref="B9" si="1">G9</f>
+        <v>EE</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -700,6 +828,109 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF3F30C-664B-4BE6-A95F-65B20E251DA6}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="str">
+        <f xml:space="preserve"> VLOOKUP(B4, IF({0,1},card!A:A,card!B:B), 2, FALSE)</f>
+        <v>300301101</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="str">
+        <f xml:space="preserve"> VLOOKUP(B5, IF({0,1},card!A:A,card!B:B), 2, FALSE)</f>
+        <v>300401101</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="str">
+        <f xml:space="preserve"> VLOOKUP(B6, IF({0,1},card!A:A,card!B:B), 2, FALSE)</f>
+        <v>300201101</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="str">
+        <f xml:space="preserve"> VLOOKUP(B7, IF({0,1},card!A:A,card!B:B), 2, FALSE)</f>
+        <v>300501101</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="str">
+        <f xml:space="preserve"> VLOOKUP(B8, IF({0,1},card!A:A,card!B:B), 2, FALSE)</f>
+        <v>300101101</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964738F3-8024-4E2A-84BD-E3D75A928311}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
